--- a/Export_Vorlage/Schächte.xlsx
+++ b/Export_Vorlage/Schächte.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schaechte" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Schaechte" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schaechte'!$A$26:$Q$5000</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Schaechte'!$25:$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Schaechte'!$26:$26,'Schaechte'!$A:$C</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -19,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;CHF&quot; #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0&quot; Schächte&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -397,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -485,6 +486,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -770,13 +783,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -796,10 +809,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -816,10 +829,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF6600"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -836,10 +849,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -856,10 +869,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="AEB135"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -876,10 +889,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="92D050"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -895,8 +908,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -945,10 +958,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -957,13 +970,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -983,10 +996,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="92D050"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1003,10 +1016,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E7E6E6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1023,10 +1036,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1042,8 +1055,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1092,10 +1105,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1104,13 +1117,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1130,10 +1143,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="548235"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1150,10 +1163,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1170,10 +1183,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF8000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1190,10 +1203,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00B0F0"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1210,10 +1223,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1229,8 +1242,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1279,10 +1292,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1291,13 +1304,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1317,10 +1330,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="548235"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1337,10 +1350,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="BF8F00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1357,10 +1370,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00B0F0"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1377,10 +1390,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1397,10 +1410,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="D6DCE4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1416,8 +1429,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1466,10 +1479,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1478,13 +1491,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1504,10 +1517,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1524,10 +1537,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00B050"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1544,10 +1557,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="D6DCE4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1563,8 +1576,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1613,10 +1626,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1625,13 +1638,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1651,17 +1664,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4472C4"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1669,10 +1682,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8497B0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1680,10 +1693,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="D6DCE4"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1702,8 +1715,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="0"/>
               </a:pPr>
@@ -1734,8 +1747,8 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="700" b="0"/>
             </a:pPr>
@@ -1764,10 +1777,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1776,13 +1789,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1802,17 +1815,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9DC3E6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1820,10 +1833,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="76A5AF"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1831,10 +1844,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4472C4"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1842,10 +1855,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="2F5597"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1853,10 +1866,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8497B0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1864,10 +1877,10 @@
           <dPt>
             <idx val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="44546A"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1886,8 +1899,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="0"/>
               </a:pPr>
@@ -1918,8 +1931,8 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="700" b="0"/>
             </a:pPr>
@@ -1948,10 +1961,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1960,121 +1973,121 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="3024000" y="72000"/>
-    <ext cx="4680000" cy="558000"/>
+    <pos x="2419200" y="72000"/>
+    <ext cx="3744000" cy="558000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="3024000" y="630000"/>
-    <ext cx="4680000" cy="558000"/>
+    <pos x="2419200" y="630000"/>
+    <ext cx="3744000" cy="558000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="3024000" y="1188000"/>
-    <ext cx="4680000" cy="558000"/>
+    <pos x="2419200" y="1188000"/>
+    <ext cx="3744000" cy="558000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="3024000" y="1746000"/>
-    <ext cx="4680000" cy="558000"/>
+    <pos x="2419200" y="1746000"/>
+    <ext cx="3744000" cy="558000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="3024000" y="2304000"/>
-    <ext cx="4680000" cy="558000"/>
+    <pos x="2419200" y="2304000"/>
+    <ext cx="3744000" cy="558000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848000" y="72000"/>
-    <ext cx="3600000" cy="2790000"/>
+    <pos x="6278400" y="72000"/>
+    <ext cx="2880000" cy="2790000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11556000" y="72000"/>
-    <ext cx="3600000" cy="2790000"/>
+    <pos x="9244800" y="72000"/>
+    <ext cx="2880000" cy="2790000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2089,13 +2102,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2540,7 +2553,7 @@
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="12">
-        <f>COUNTIF($F$27:$F$5000,"0")</f>
+        <f>COUNTIF('Schaechte'!$F$27:$F$5000,"0")</f>
         <v/>
       </c>
       <c r="D17" s="13" t="inlineStr">
@@ -2550,7 +2563,7 @@
       </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="12">
-        <f>COUNTIF($B$27:$B$5000,"Kontrollschacht")</f>
+        <f>COUNTIF('Schaechte'!$B$27:$B$5000,"Kontrollschacht")</f>
         <v/>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2560,7 +2573,7 @@
       </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="12">
-        <f>COUNTIF($G$27:$G$5000,"Ja")</f>
+        <f>COUNTIF('Schaechte'!$G$27:$G$5000,"Ja")</f>
         <v/>
       </c>
       <c r="J17" s="15" t="inlineStr">
@@ -2569,7 +2582,7 @@
         </is>
       </c>
       <c r="K17" s="12">
-        <f>COUNTIF($J$27:$J$5000,"Abwasser Uri")+COUNTIF($J$27:$J$5000,"AWU")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Abwasser Uri")+COUNTIF('Schaechte'!$J$27:$J$5000,"AWU")</f>
         <v/>
       </c>
       <c r="L17" s="15" t="inlineStr">
@@ -2578,7 +2591,7 @@
         </is>
       </c>
       <c r="M17" s="12">
-        <f>COUNTIF($K$27:$K$5000,"Abwasser Uri")</f>
+        <f>COUNTIF('Schaechte'!$K$27:$K$5000,"Abwasser Uri")</f>
         <v/>
       </c>
       <c r="N17" s="16" t="inlineStr">
@@ -2587,7 +2600,7 @@
         </is>
       </c>
       <c r="O17" s="12">
-        <f>COUNTIF($O$27:$O$5000,"A15")</f>
+        <f>COUNTIF('Schaechte'!$O$27:$O$5000,"A15")</f>
         <v/>
       </c>
       <c r="P17" s="11" t="inlineStr">
@@ -2596,7 +2609,7 @@
         </is>
       </c>
       <c r="Q17" s="12">
-        <f>COUNTIF($P$27:$P$5000,"offen")</f>
+        <f>COUNTIF('Schaechte'!$P$27:$P$5000,"offen")</f>
         <v/>
       </c>
     </row>
@@ -2608,7 +2621,7 @@
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="12">
-        <f>COUNTIF($F$27:$F$5000,"1")</f>
+        <f>COUNTIF('Schaechte'!$F$27:$F$5000,"1")</f>
         <v/>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -2618,7 +2631,7 @@
       </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="12">
-        <f>COUNTIF($B$27:$B$5000,"Einstiegschacht")</f>
+        <f>COUNTIF('Schaechte'!$B$27:$B$5000,"Einstiegschacht")</f>
         <v/>
       </c>
       <c r="G18" s="19" t="inlineStr">
@@ -2628,7 +2641,7 @@
       </c>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="12">
-        <f>COUNTIF($G$27:$G$5000,"Nein")</f>
+        <f>COUNTIF('Schaechte'!$G$27:$G$5000,"Nein")</f>
         <v/>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -2637,7 +2650,7 @@
         </is>
       </c>
       <c r="K18" s="12">
-        <f>COUNTIF($J$27:$J$5000,"Kanton Uri")+COUNTIF($J$27:$J$5000,"Kanton")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Kanton Uri")+COUNTIF('Schaechte'!$J$27:$J$5000,"Kanton")</f>
         <v/>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -2646,7 +2659,7 @@
         </is>
       </c>
       <c r="M18" s="12">
-        <f>COUNTIF($K$27:$K$5000,"Kanalsanierer")</f>
+        <f>COUNTIF('Schaechte'!$K$27:$K$5000,"Kanalsanierer")</f>
         <v/>
       </c>
       <c r="N18" s="16" t="inlineStr">
@@ -2655,7 +2668,7 @@
         </is>
       </c>
       <c r="O18" s="12">
-        <f>COUNTIF($O$27:$O$5000,"B125")</f>
+        <f>COUNTIF('Schaechte'!$O$27:$O$5000,"B125")</f>
         <v/>
       </c>
       <c r="P18" s="22" t="inlineStr">
@@ -2664,7 +2677,7 @@
         </is>
       </c>
       <c r="Q18" s="12">
-        <f>COUNTIF($P$27:$P$5000,"abgeschlossen")</f>
+        <f>COUNTIF('Schaechte'!$P$27:$P$5000,"abgeschlossen")</f>
         <v/>
       </c>
     </row>
@@ -2676,7 +2689,7 @@
       </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="12">
-        <f>COUNTIF($F$27:$F$5000,"2")</f>
+        <f>COUNTIF('Schaechte'!$F$27:$F$5000,"2")</f>
         <v/>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -2686,7 +2699,7 @@
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="12">
-        <f>COUNTA($B$27:$B$5000)-COUNTIF($B$27:$B$5000,"Kontrollschacht")-COUNTIF($B$27:$B$5000,"Einstiegschacht")</f>
+        <f>COUNTA('Schaechte'!$B$27:$B$5000)-COUNTIF('Schaechte'!$B$27:$B$5000,"Kontrollschacht")-COUNTIF('Schaechte'!$B$27:$B$5000,"Einstiegschacht")</f>
         <v/>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -2696,7 +2709,7 @@
       </c>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="12">
-        <f>COUNTIF($G$27:$G$5000,"U")</f>
+        <f>COUNTIF('Schaechte'!$G$27:$G$5000,"U")</f>
         <v/>
       </c>
       <c r="J19" s="24" t="inlineStr">
@@ -2705,7 +2718,7 @@
         </is>
       </c>
       <c r="K19" s="12">
-        <f>COUNTIF($J$27:$J$5000,"Bund")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Bund")</f>
         <v/>
       </c>
       <c r="L19" s="25" t="inlineStr">
@@ -2714,7 +2727,7 @@
         </is>
       </c>
       <c r="M19" s="12">
-        <f>COUNTIF($K$27:$K$5000,"Baumeister")</f>
+        <f>COUNTIF('Schaechte'!$K$27:$K$5000,"Baumeister")</f>
         <v/>
       </c>
       <c r="N19" s="16" t="inlineStr">
@@ -2723,7 +2736,7 @@
         </is>
       </c>
       <c r="O19" s="12">
-        <f>COUNTIF($O$27:$O$5000,"C250")</f>
+        <f>COUNTIF('Schaechte'!$O$27:$O$5000,"C250")</f>
         <v/>
       </c>
       <c r="P19" s="23" t="inlineStr">
@@ -2732,7 +2745,7 @@
         </is>
       </c>
       <c r="Q19" s="12">
-        <f>COUNTA($C$27:$C$5000)-COUNTA($P$27:$P$5000)</f>
+        <f>COUNTA('Schaechte'!$C$27:$C$5000)-COUNTA('Schaechte'!$P$27:$P$5000)</f>
         <v/>
       </c>
     </row>
@@ -2744,7 +2757,7 @@
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="12">
-        <f>COUNTIF($F$27:$F$5000,"3")</f>
+        <f>COUNTIF('Schaechte'!$F$27:$F$5000,"3")</f>
         <v/>
       </c>
       <c r="D20" s="5" t="n"/>
@@ -2759,7 +2772,7 @@
         </is>
       </c>
       <c r="K20" s="12">
-        <f>COUNTIF($J$27:$J$5000,"Gemeinde")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Gemeinde")</f>
         <v/>
       </c>
       <c r="L20" s="27" t="inlineStr">
@@ -2768,7 +2781,7 @@
         </is>
       </c>
       <c r="M20" s="12">
-        <f>COUNTIF($K$27:$K$5000,"Gartenbauer")</f>
+        <f>COUNTIF('Schaechte'!$K$27:$K$5000,"Gartenbauer")</f>
         <v/>
       </c>
       <c r="N20" s="16" t="inlineStr">
@@ -2777,7 +2790,7 @@
         </is>
       </c>
       <c r="O20" s="12">
-        <f>COUNTIF($O$27:$O$5000,"D400")</f>
+        <f>COUNTIF('Schaechte'!$O$27:$O$5000,"D400")</f>
         <v/>
       </c>
       <c r="P20" s="5" t="n"/>
@@ -2791,7 +2804,7 @@
       </c>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="12">
-        <f>COUNTIF($F$27:$F$5000,"4")</f>
+        <f>COUNTIF('Schaechte'!$F$27:$F$5000,"4")</f>
         <v/>
       </c>
       <c r="D21" s="5" t="n"/>
@@ -2806,7 +2819,7 @@
         </is>
       </c>
       <c r="K21" s="12">
-        <f>COUNTIF($J$27:$J$5000,"Privat")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Privat")</f>
         <v/>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -2815,7 +2828,7 @@
         </is>
       </c>
       <c r="M21" s="12">
-        <f>COUNTA($C$27:$C$5000)-COUNTA($K$27:$K$5000)</f>
+        <f>COUNTA('Schaechte'!$C$27:$C$5000)-COUNTA('Schaechte'!$K$27:$K$5000)</f>
         <v/>
       </c>
       <c r="N21" s="16" t="inlineStr">
@@ -2824,7 +2837,7 @@
         </is>
       </c>
       <c r="O21" s="12">
-        <f>COUNTIF($O$27:$O$5000,"E600")</f>
+        <f>COUNTIF('Schaechte'!$O$27:$O$5000,"E600")</f>
         <v/>
       </c>
       <c r="P21" s="5" t="n"/>
@@ -2850,7 +2863,7 @@
         </is>
       </c>
       <c r="O22" s="12">
-        <f>COUNTIF($O$27:$O$5000,"F900")</f>
+        <f>COUNTIF('Schaechte'!$O$27:$O$5000,"F900")</f>
         <v/>
       </c>
       <c r="P22" s="5" t="n"/>
@@ -2864,7 +2877,7 @@
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="29">
-        <f>COUNTA($C$27:$C$5000)</f>
+        <f>COUNTA('Schaechte'!$C$27:$C$5000)</f>
         <v/>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -2874,7 +2887,7 @@
       </c>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="29">
-        <f>COUNTA($B$27:$B$5000)</f>
+        <f>COUNTA('Schaechte'!$B$27:$B$5000)</f>
         <v/>
       </c>
       <c r="G23" s="28" t="inlineStr">
@@ -2884,7 +2897,7 @@
       </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="30">
-        <f>SUM($I$27:$I$5000)</f>
+        <f>SUM('Schaechte'!$I$27:$I$5000)</f>
         <v/>
       </c>
       <c r="J23" s="31" t="inlineStr">
@@ -2893,7 +2906,7 @@
         </is>
       </c>
       <c r="K23" s="29">
-        <f>COUNTA($J$27:$J$5000)</f>
+        <f>COUNTA('Schaechte'!$J$27:$J$5000)</f>
         <v/>
       </c>
       <c r="L23" s="31" t="inlineStr">
@@ -2902,7 +2915,7 @@
         </is>
       </c>
       <c r="M23" s="29">
-        <f>COUNTA($C$27:$C$5000)</f>
+        <f>COUNTA('Schaechte'!$C$27:$C$5000)</f>
         <v/>
       </c>
       <c r="N23" s="31" t="inlineStr">
@@ -2911,7 +2924,7 @@
         </is>
       </c>
       <c r="O23" s="29">
-        <f>SUM($N$27:$N$5000)</f>
+        <f>SUM('Schaechte'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="P23" s="31" t="inlineStr">
@@ -2920,121 +2933,144 @@
         </is>
       </c>
       <c r="Q23" s="29">
-        <f>COUNTA($C$27:$C$5000)</f>
+        <f>COUNTA('Schaechte'!$C$27:$C$5000)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="5" customHeight="1"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>Aktuelle Auswahl</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="33">
+        <f>SUBTOTAL(103,$A$27:$A$5000)</f>
+        <v/>
+      </c>
+      <c r="D24" s="32" t="n"/>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="32" t="inlineStr">
+        <is>
+          <t>Kosten CHF</t>
+        </is>
+      </c>
+      <c r="H24" s="35">
+        <f>SUBTOTAL(109,$I$27:$I$5000)</f>
+        <v/>
+      </c>
+    </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="32" t="inlineStr"/>
-      <c r="B25" s="33" t="n"/>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="33" t="n"/>
-      <c r="F25" s="33" t="n"/>
-      <c r="G25" s="33" t="n"/>
-      <c r="H25" s="33" t="n"/>
-      <c r="I25" s="33" t="n"/>
-      <c r="J25" s="33" t="n"/>
-      <c r="K25" s="33" t="n"/>
-      <c r="L25" s="33" t="n"/>
-      <c r="M25" s="33" t="n"/>
-      <c r="N25" s="34" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr"/>
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="37" t="n"/>
+      <c r="G25" s="37" t="n"/>
+      <c r="H25" s="37" t="n"/>
+      <c r="I25" s="37" t="n"/>
+      <c r="J25" s="37" t="n"/>
+      <c r="K25" s="37" t="n"/>
+      <c r="L25" s="37" t="n"/>
+      <c r="M25" s="37" t="n"/>
+      <c r="N25" s="38" t="inlineStr">
         <is>
           <t>Ausmass</t>
         </is>
       </c>
-      <c r="O25" s="35" t="n"/>
-      <c r="P25" s="34" t="inlineStr">
+      <c r="O25" s="39" t="n"/>
+      <c r="P25" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q25" s="35" t="n"/>
+      <c r="Q25" s="39" t="n"/>
     </row>
     <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>NR.</t>
         </is>
       </c>
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>Funktion</t>
         </is>
       </c>
-      <c r="C26" s="36" t="inlineStr">
+      <c r="C26" s="40" t="inlineStr">
         <is>
           <t>Schachtnummer</t>
         </is>
       </c>
-      <c r="D26" s="36" t="inlineStr">
+      <c r="D26" s="40" t="inlineStr">
         <is>
           <t>Strasse</t>
         </is>
       </c>
-      <c r="E26" s="36" t="inlineStr">
+      <c r="E26" s="40" t="inlineStr">
         <is>
           <t>Primäre Schäden</t>
         </is>
       </c>
-      <c r="F26" s="36" t="inlineStr">
+      <c r="F26" s="40" t="inlineStr">
         <is>
           <t>Zustandsklasse</t>
         </is>
       </c>
-      <c r="G26" s="36" t="inlineStr">
+      <c r="G26" s="40" t="inlineStr">
         <is>
           <t>Ja/Nein</t>
         </is>
       </c>
-      <c r="H26" s="36" t="inlineStr">
+      <c r="H26" s="40" t="inlineStr">
         <is>
           <t>Massnahmen</t>
         </is>
       </c>
-      <c r="I26" s="36" t="inlineStr">
+      <c r="I26" s="40" t="inlineStr">
         <is>
           <t>Kosten</t>
         </is>
       </c>
-      <c r="J26" s="36" t="inlineStr">
+      <c r="J26" s="40" t="inlineStr">
         <is>
           <t>Eigentümer</t>
         </is>
       </c>
-      <c r="K26" s="36" t="inlineStr">
+      <c r="K26" s="40" t="inlineStr">
         <is>
           <t>Ausgeführt durch</t>
         </is>
       </c>
-      <c r="L26" s="36" t="inlineStr">
+      <c r="L26" s="40" t="inlineStr">
         <is>
           <t>Bemerkungen</t>
         </is>
       </c>
-      <c r="M26" s="36" t="inlineStr">
+      <c r="M26" s="40" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="N26" s="36" t="inlineStr">
+      <c r="N26" s="40" t="inlineStr">
         <is>
           <t>Abdeckung Stk.</t>
         </is>
       </c>
-      <c r="O26" s="36" t="inlineStr">
+      <c r="O26" s="40" t="inlineStr">
         <is>
           <t>Belastungsklasse</t>
         </is>
       </c>
-      <c r="P26" s="36" t="inlineStr">
+      <c r="P26" s="40" t="inlineStr">
         <is>
           <t>Status
 offen/abgeschlossen</t>
         </is>
       </c>
-      <c r="Q26" s="36" t="inlineStr">
+      <c r="Q26" s="40" t="inlineStr">
         <is>
           <t>Ausführung
 Datum/Jahr</t>
@@ -3042,27 +3078,28 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="37" t="n"/>
-      <c r="B27" s="38" t="n"/>
-      <c r="C27" s="37" t="n"/>
-      <c r="D27" s="38" t="n"/>
-      <c r="E27" s="39" t="n"/>
-      <c r="F27" s="37" t="n"/>
-      <c r="G27" s="37" t="n"/>
-      <c r="H27" s="39" t="n"/>
-      <c r="I27" s="40" t="n"/>
-      <c r="J27" s="37" t="n"/>
-      <c r="K27" s="37" t="n"/>
-      <c r="L27" s="39" t="n"/>
-      <c r="M27" s="41" t="n"/>
-      <c r="N27" s="42" t="n"/>
-      <c r="O27" s="37" t="n"/>
-      <c r="P27" s="37" t="n"/>
-      <c r="Q27" s="37" t="n"/>
+      <c r="A27" s="41" t="n"/>
+      <c r="B27" s="42" t="n"/>
+      <c r="C27" s="41" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="43" t="n"/>
+      <c r="F27" s="41" t="n"/>
+      <c r="G27" s="41" t="n"/>
+      <c r="H27" s="43" t="n"/>
+      <c r="I27" s="44" t="n"/>
+      <c r="J27" s="41" t="n"/>
+      <c r="K27" s="41" t="n"/>
+      <c r="L27" s="43" t="n"/>
+      <c r="M27" s="45" t="n"/>
+      <c r="N27" s="46" t="n"/>
+      <c r="O27" s="41" t="n"/>
+      <c r="P27" s="41" t="n"/>
+      <c r="Q27" s="41" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A26:Q5000"/>
-  <mergeCells count="29">
+  <mergeCells count="30">
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="L16:M16"/>
@@ -3183,7 +3220,7 @@
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>

--- a/Export_Vorlage/Schächte.xlsx
+++ b/Export_Vorlage/Schächte.xlsx
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="K17" s="12">
-        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Abwasser Uri")+COUNTIF('Schaechte'!$J$27:$J$5000,"AWU")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Abwasser Uri")+COUNTIF('Schaechte'!$J$27:$J$5000,"AWU")+COUNTIF('Schaechte'!$J$27:$J$5000,"AWU_von_oeffentlich")+COUNTIF('Schaechte'!$J$27:$J$5000,"AWU_von_oeffentlich (Abwasserverband)")+COUNTIF('Schaechte'!$J$27:$J$5000,"AWU_von_privat")+COUNTIF('Schaechte'!$J$27:$J$5000,"AWU_von_privat (Abwasserverband)")</f>
         <v/>
       </c>
       <c r="L17" s="15" t="inlineStr">
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="K18" s="12">
-        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Kanton Uri")+COUNTIF('Schaechte'!$J$27:$J$5000,"Kanton")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Kanton Uri")+COUNTIF('Schaechte'!$J$27:$J$5000,"Kanton")+COUNTIF('Schaechte'!$J$27:$J$5000,"Kanton Uri (Kanton)")</f>
         <v/>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="K19" s="12">
-        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Bund")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Bund")+COUNTIF('Schaechte'!$J$27:$J$5000,"Bund Astra")+COUNTIF('Schaechte'!$J$27:$J$5000,"Bund Astra (Bund)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Bund (Bund)")</f>
         <v/>
       </c>
       <c r="L19" s="25" t="inlineStr">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="K20" s="12">
-        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Gemeinde")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Gemeinde")+COUNTIF('Schaechte'!$J$27:$J$5000,"Altdorf")+COUNTIF('Schaechte'!$J$27:$J$5000,"Altdorf (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Bürglen")+COUNTIF('Schaechte'!$J$27:$J$5000,"Bürglen (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Schattdorf")+COUNTIF('Schaechte'!$J$27:$J$5000,"Schattdorf (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Andermatt")+COUNTIF('Schaechte'!$J$27:$J$5000,"Andermatt (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Attinghausen")+COUNTIF('Schaechte'!$J$27:$J$5000,"Attinghausen (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Erstfeld")+COUNTIF('Schaechte'!$J$27:$J$5000,"Erstfeld (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Flüelen")+COUNTIF('Schaechte'!$J$27:$J$5000,"Flüelen (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Göschenen")+COUNTIF('Schaechte'!$J$27:$J$5000,"Göschenen (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Gurtnellen")+COUNTIF('Schaechte'!$J$27:$J$5000,"Gurtnellen (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Hospental")+COUNTIF('Schaechte'!$J$27:$J$5000,"Hospental (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Isenthal")+COUNTIF('Schaechte'!$J$27:$J$5000,"Isenthal (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Realp")+COUNTIF('Schaechte'!$J$27:$J$5000,"Realp (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Seedorf")+COUNTIF('Schaechte'!$J$27:$J$5000,"Seedorf (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Seelisberg")+COUNTIF('Schaechte'!$J$27:$J$5000,"Seelisberg (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Silenen")+COUNTIF('Schaechte'!$J$27:$J$5000,"Silenen (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Sisikon")+COUNTIF('Schaechte'!$J$27:$J$5000,"Sisikon (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Spiringen")+COUNTIF('Schaechte'!$J$27:$J$5000,"Spiringen (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Unterschächen")+COUNTIF('Schaechte'!$J$27:$J$5000,"Unterschächen (Gemeinde)")+COUNTIF('Schaechte'!$J$27:$J$5000,"Wassen")+COUNTIF('Schaechte'!$J$27:$J$5000,"Wassen (Gemeinde)")</f>
         <v/>
       </c>
       <c r="L20" s="27" t="inlineStr">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="K21" s="12">
-        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Privat")</f>
+        <f>COUNTIF('Schaechte'!$J$27:$J$5000,"Privat")+COUNTIF('Schaechte'!$J$27:$J$5000,"Privat (Privat)")+COUNTIF('Schaechte'!$J$27:$J$5000,"RUAG")+COUNTIF('Schaechte'!$J$27:$J$5000,"RUAG (Privat)")</f>
         <v/>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -3190,32 +3190,179 @@
     <cfRule type="expression" priority="17" dxfId="0" stopIfTrue="1">
       <formula>$J27="AWU"</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" dxfId="6" stopIfTrue="1">
+    <cfRule type="expression" priority="18" dxfId="0" stopIfTrue="1">
+      <formula>$J27="AWU_von_oeffentlich"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="19" dxfId="0" stopIfTrue="1">
+      <formula>$J27="AWU_von_oeffentlich (Abwasserverband)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" dxfId="0" stopIfTrue="1">
+      <formula>$J27="AWU_von_privat"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="21" dxfId="0" stopIfTrue="1">
+      <formula>$J27="AWU_von_privat (Abwasserverband)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="22" dxfId="6" stopIfTrue="1">
       <formula>$J27="Kanton Uri"</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" dxfId="6" stopIfTrue="1">
+    <cfRule type="expression" priority="23" dxfId="6" stopIfTrue="1">
       <formula>$J27="Kanton"</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" dxfId="10" stopIfTrue="1">
+    <cfRule type="expression" priority="24" dxfId="6" stopIfTrue="1">
+      <formula>$J27="Kanton Uri (Kanton)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="25" dxfId="10" stopIfTrue="1">
       <formula>$J27="Bund"</formula>
     </cfRule>
-    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="26" dxfId="10" stopIfTrue="1">
+      <formula>$J27="Bund Astra"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" dxfId="10" stopIfTrue="1">
+      <formula>$J27="Bund Astra (Bund)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="28" dxfId="10" stopIfTrue="1">
+      <formula>$J27="Bund (Bund)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="29" dxfId="2" stopIfTrue="1">
       <formula>$J27="Gemeinde"</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="30" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Altdorf"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="31" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Altdorf (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="32" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Bürglen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="33" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Bürglen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="34" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Schattdorf"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Schattdorf (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Andermatt"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="37" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Andermatt (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="38" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Attinghausen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="39" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Attinghausen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="40" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Erstfeld"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="41" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Erstfeld (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="42" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Flüelen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="43" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Flüelen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="44" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Göschenen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="45" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Göschenen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="46" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Gurtnellen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="47" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Gurtnellen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="48" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Hospental"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="49" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Hospental (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="50" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Isenthal"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="51" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Isenthal (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="52" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Realp"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="53" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Realp (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="54" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Seedorf"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="55" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Seedorf (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="56" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Seelisberg"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="57" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Seelisberg (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="58" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Silenen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="59" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Silenen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="60" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Sisikon"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="61" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Sisikon (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="62" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Spiringen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="63" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Spiringen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="64" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Unterschächen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="65" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Unterschächen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="66" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Wassen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="67" dxfId="2" stopIfTrue="1">
+      <formula>$J27="Wassen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="68" dxfId="4" stopIfTrue="1">
       <formula>$J27="Privat"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="69" dxfId="4" stopIfTrue="1">
+      <formula>$J27="Privat (Privat)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="70" dxfId="4" stopIfTrue="1">
+      <formula>$J27="RUAG"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="71" dxfId="4" stopIfTrue="1">
+      <formula>$J27="RUAG (Privat)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P27:P5000">
-    <cfRule type="expression" priority="23" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="72" dxfId="4" stopIfTrue="1">
       <formula>$P27="offen"</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" dxfId="11" stopIfTrue="1">
+    <cfRule type="expression" priority="73" dxfId="11" stopIfTrue="1">
       <formula>$P27="abgeschlossen"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:Q5000">
-    <cfRule type="expression" priority="25" dxfId="12">
+    <cfRule type="expression" priority="74" dxfId="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
